--- a/diseases/d165/1995-1999.xlsx
+++ b/diseases/d165/1995-1999.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>13</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1158,9 +1155,6 @@
       <c r="O4" t="n">
         <v>6</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1551,9 +1545,6 @@
       <c r="O6" t="n">
         <v>3</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1944,9 +1935,6 @@
       <c r="O8" t="n">
         <v>13</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2337,9 +2325,6 @@
       <c r="O10" t="n">
         <v>5</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -2730,9 +2715,6 @@
       <c r="O12" t="n">
         <v>10</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3123,9 +3105,6 @@
       <c r="O14" t="n">
         <v>12</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="S14" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3516,9 +3495,6 @@
       <c r="O16" t="n">
         <v>12</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="S16" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -3909,9 +3885,6 @@
       <c r="O18" t="n">
         <v>13</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="S18" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4302,9 +4275,6 @@
       <c r="O20" t="n">
         <v>7</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="S20" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -4695,9 +4665,6 @@
       <c r="O22" t="n">
         <v>10</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="S22" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5088,9 +5055,6 @@
       <c r="O24" t="n">
         <v>8</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="S24" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5481,9 +5445,6 @@
       <c r="O26" t="n">
         <v>5</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="S26" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5874,9 +5835,6 @@
       <c r="O28" t="n">
         <v>6</v>
       </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
       <c r="S28" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6267,9 +6225,6 @@
       <c r="O30" t="n">
         <v>9</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="S30" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -6660,9 +6615,6 @@
       <c r="O32" t="n">
         <v>15</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="S32" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7053,9 +7005,6 @@
       <c r="O34" t="n">
         <v>15</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="S34" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7446,9 +7395,6 @@
       <c r="O36" t="n">
         <v>7</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="S36" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -7839,9 +7785,6 @@
       <c r="O38" t="n">
         <v>10</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="S38" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8232,9 +8175,6 @@
       <c r="O40" t="n">
         <v>7</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="S40" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -8625,9 +8565,6 @@
       <c r="O42" t="n">
         <v>9</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="S42" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9018,9 +8955,6 @@
       <c r="O44" t="n">
         <v>15</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="S44" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9411,9 +9345,6 @@
       <c r="O46" t="n">
         <v>12</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="S46" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9804,9 +9735,6 @@
       <c r="O48" t="n">
         <v>12</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="S48" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10197,9 +10125,6 @@
       <c r="O50" t="n">
         <v>17</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="S50" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -10735,9 +10660,6 @@
       <c r="O53" t="n">
         <v>16</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="S53" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11273,9 +11195,6 @@
       <c r="O56" t="n">
         <v>4</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="S56" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -11811,9 +11730,6 @@
       <c r="O59" t="n">
         <v>21</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="S59" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12349,9 +12265,6 @@
       <c r="O62" t="n">
         <v>11</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="S62" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -12887,9 +12800,6 @@
       <c r="O65" t="n">
         <v>13</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="S65" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13425,9 +13335,6 @@
       <c r="O68" t="n">
         <v>18</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="S68" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -13963,9 +13870,6 @@
       <c r="O71" t="n">
         <v>19</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="S71" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -14501,9 +14405,6 @@
       <c r="O74" t="n">
         <v>9</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="S74" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15039,9 +14940,6 @@
       <c r="O77" t="n">
         <v>11</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="S77" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15577,9 +15475,6 @@
       <c r="O80" t="n">
         <v>15</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="S80" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16115,9 +16010,6 @@
       <c r="O83" t="n">
         <v>9</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="S83" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -16653,9 +16545,6 @@
       <c r="O86" t="n">
         <v>8</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="S86" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17191,9 +17080,6 @@
       <c r="O89" t="n">
         <v>6</v>
       </c>
-      <c r="Q89" t="n">
-        <v>0</v>
-      </c>
       <c r="S89" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -17729,9 +17615,6 @@
       <c r="O92" t="n">
         <v>3</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="S92" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18267,9 +18150,6 @@
       <c r="O95" t="n">
         <v>10</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="S95" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -18805,9 +18685,6 @@
       <c r="O98" t="n">
         <v>7</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="S98" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19343,9 +19220,6 @@
       <c r="O101" t="n">
         <v>12</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="S101" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -19881,9 +19755,6 @@
       <c r="O104" t="n">
         <v>18</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="S104" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20419,9 +20290,6 @@
       <c r="O107" t="n">
         <v>13</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="S107" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -20957,9 +20825,6 @@
       <c r="O110" t="n">
         <v>9</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="S110" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21495,9 +21360,6 @@
       <c r="O113" t="n">
         <v>7</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="S113" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22033,9 +21895,6 @@
       <c r="O116" t="n">
         <v>11</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="S116" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -22571,9 +22430,6 @@
       <c r="O119" t="n">
         <v>8</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="S119" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23109,9 +22965,6 @@
       <c r="O122" t="n">
         <v>8</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="S122" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -23647,9 +23500,6 @@
       <c r="O125" t="n">
         <v>8</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="S125" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24185,9 +24035,6 @@
       <c r="O128" t="n">
         <v>10</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="S128" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -24723,9 +24570,6 @@
       <c r="O131" t="n">
         <v>8</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="S131" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25261,9 +25105,6 @@
       <c r="O134" t="n">
         <v>10</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="S134" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -25799,9 +25640,6 @@
       <c r="O137" t="n">
         <v>13</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="S137" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26337,9 +26175,6 @@
       <c r="O140" t="n">
         <v>10</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="S140" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -26875,9 +26710,6 @@
       <c r="O143" t="n">
         <v>11</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="S143" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27413,9 +27245,6 @@
       <c r="O146" t="n">
         <v>5</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="S146" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -27951,9 +27780,6 @@
       <c r="O149" t="n">
         <v>6</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="S149" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -28489,9 +28315,6 @@
       <c r="O152" t="n">
         <v>10</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="S152" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -29026,9 +28849,6 @@
       </c>
       <c r="O155" t="n">
         <v>13</v>
-      </c>
-      <c r="Q155" t="n">
-        <v>0</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
